--- a/consolidacion/data/pruebas/personas_jornada4_20260816_0700.xlsx
+++ b/consolidacion/data/pruebas/personas_jornada4_20260816_0700.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -14300,7 +14300,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Vivienda</t>
+          <t>Secretaría de Vivienda</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
